--- a/education_forms/038_semiotics_knowledge_quiz--education_forms.xlsx
+++ b/education_forms/038_semiotics_knowledge_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_0</t>
+          <t>option 0</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_0</t>
+          <t>option 0</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_0</t>
+          <t>option 0</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_0</t>
+          <t>option 0</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_0</t>
+          <t>option 0</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option_0</t>
+          <t>option 0</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option_0</t>
+          <t>option 0</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option_0</t>
+          <t>option 0</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
